--- a/research/traditional_assets/database/data/luxembourg/luxembourg_electrical_equipment.xlsx
+++ b/research/traditional_assets/database/data/luxembourg/luxembourg_electrical_equipment.xlsx
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="K2">
-        <v>-70.59999999999999</v>
+        <v>-152.1</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.0008659079663532905</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>-0.006903353057199212</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -609,61 +609,70 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.05</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>622.6</v>
+        <v>416.4</v>
       </c>
       <c r="V2">
-        <v>0.476576852418861</v>
+        <v>0.3433943592281049</v>
+      </c>
+      <c r="W2">
+        <v>-0.2608919382504288</v>
       </c>
       <c r="X2">
-        <v>0.0583319668135158</v>
+        <v>0.1045295470348424</v>
+      </c>
+      <c r="Y2">
+        <v>-0.3654214852852712</v>
       </c>
       <c r="AB2">
-        <v>0.0583319668135158</v>
+        <v>0.1040172433283613</v>
       </c>
       <c r="AD2">
         <v>0</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>9.902398459282114</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>9.902398459282114</v>
       </c>
       <c r="AG2">
-        <v>-622.6</v>
+        <v>-406.4976015407179</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>0.008100105547246446</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>0.02353218160243042</v>
       </c>
       <c r="AJ2">
-        <v>-0.910500146241591</v>
+        <v>-0.5042753902204782</v>
       </c>
       <c r="AK2">
-        <v>15.72222222222221</v>
+        <v>-92.33548605389205</v>
       </c>
       <c r="AL2">
-        <v>0.001</v>
+        <v>0.045</v>
       </c>
       <c r="AM2">
-        <v>-0.078</v>
+        <v>-0.345</v>
       </c>
       <c r="AN2">
         <v>-0</v>
       </c>
       <c r="AO2">
-        <v>-62500</v>
+        <v>-2337.777777777778</v>
       </c>
       <c r="AP2">
-        <v>9.961600000000001</v>
+        <v>3.943133199541351</v>
       </c>
       <c r="AQ2">
-        <v>801.2820512820513</v>
+        <v>304.9275362318841</v>
       </c>
     </row>
     <row r="3">
@@ -683,16 +692,16 @@
         </is>
       </c>
       <c r="K3">
-        <v>-70.59999999999999</v>
+        <v>-152.1</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>1.05</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.0008659079663532905</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0.006903353057199212</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -704,61 +713,70 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.05</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>622.6</v>
+        <v>416.4</v>
       </c>
       <c r="V3">
-        <v>0.476576852418861</v>
+        <v>0.3433943592281049</v>
+      </c>
+      <c r="W3">
+        <v>-0.2608919382504288</v>
       </c>
       <c r="X3">
-        <v>0.0583319668135158</v>
+        <v>0.1045295470348424</v>
+      </c>
+      <c r="Y3">
+        <v>-0.3654214852852712</v>
       </c>
       <c r="AB3">
-        <v>0.0583319668135158</v>
+        <v>0.1040172433283613</v>
       </c>
       <c r="AD3">
         <v>0</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>9.902398459282114</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>9.902398459282114</v>
       </c>
       <c r="AG3">
-        <v>-622.6</v>
+        <v>-406.4976015407179</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.008100105547246446</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.02353218160243042</v>
       </c>
       <c r="AJ3">
-        <v>-0.910500146241591</v>
+        <v>-0.5042753902204782</v>
       </c>
       <c r="AK3">
-        <v>15.72222222222221</v>
+        <v>-92.33548605389205</v>
       </c>
       <c r="AL3">
-        <v>0.001</v>
+        <v>0.045</v>
       </c>
       <c r="AM3">
-        <v>-0.078</v>
+        <v>-0.345</v>
       </c>
       <c r="AN3">
         <v>-0</v>
       </c>
       <c r="AO3">
-        <v>-62500</v>
+        <v>-2337.777777777778</v>
       </c>
       <c r="AP3">
-        <v>9.961600000000001</v>
+        <v>3.943133199541351</v>
       </c>
       <c r="AQ3">
-        <v>801.2820512820513</v>
+        <v>304.9275362318841</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/luxembourg/luxembourg_electrical_equipment.xlsx
+++ b/research/traditional_assets/database/data/luxembourg/luxembourg_electrical_equipment.xlsx
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="K2">
-        <v>-152.1</v>
+        <v>-22.5</v>
       </c>
       <c r="M2">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.0008659079663532905</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-0.006903353057199212</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -609,70 +609,73 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>1.05</v>
-      </c>
-      <c r="T2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>416.4</v>
+        <v>299.4</v>
       </c>
       <c r="V2">
-        <v>0.3433943592281049</v>
+        <v>1.14624808575804</v>
       </c>
       <c r="W2">
-        <v>-0.2608919382504288</v>
+        <v>-0.05475784862496958</v>
       </c>
       <c r="X2">
-        <v>0.1045295470348424</v>
+        <v>0.0926791772676728</v>
       </c>
       <c r="Y2">
-        <v>-0.3654214852852712</v>
+        <v>-0.1474370258926424</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>-8.27985896318345</v>
       </c>
       <c r="AB2">
-        <v>0.1040172433283613</v>
+        <v>0.08855940134754284</v>
+      </c>
+      <c r="AC2">
+        <v>-8.368418364530994</v>
       </c>
       <c r="AD2">
         <v>0</v>
       </c>
       <c r="AE2">
-        <v>9.902398459282114</v>
+        <v>22.24039121429266</v>
       </c>
       <c r="AF2">
-        <v>9.902398459282114</v>
+        <v>22.24039121429266</v>
       </c>
       <c r="AG2">
-        <v>-406.4976015407179</v>
+        <v>-277.1596087857073</v>
       </c>
       <c r="AH2">
-        <v>0.008100105547246446</v>
+        <v>0.07846584997647002</v>
       </c>
       <c r="AI2">
-        <v>0.02353218160243042</v>
+        <v>0.03386997131438198</v>
       </c>
       <c r="AJ2">
-        <v>-0.5042753902204782</v>
+        <v>17.36631596094754</v>
       </c>
       <c r="AK2">
-        <v>-92.33548605389205</v>
+        <v>-0.7758350276227626</v>
       </c>
       <c r="AL2">
-        <v>0.045</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.345</v>
+        <v>-7.73</v>
       </c>
       <c r="AN2">
         <v>-0</v>
       </c>
-      <c r="AO2">
-        <v>-2337.777777777778</v>
-      </c>
       <c r="AP2">
-        <v>3.943133199541351</v>
+        <v>2.09874003320996</v>
       </c>
       <c r="AQ2">
-        <v>304.9275362318841</v>
+        <v>17.78783958602846</v>
       </c>
     </row>
     <row r="3">
@@ -692,16 +695,16 @@
         </is>
       </c>
       <c r="K3">
-        <v>-152.1</v>
+        <v>-22.5</v>
       </c>
       <c r="M3">
-        <v>1.05</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.0008659079663532905</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0.006903353057199212</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -713,70 +716,73 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>1.05</v>
-      </c>
-      <c r="T3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>416.4</v>
+        <v>299.4</v>
       </c>
       <c r="V3">
-        <v>0.3433943592281049</v>
+        <v>1.14624808575804</v>
       </c>
       <c r="W3">
-        <v>-0.2608919382504288</v>
+        <v>-0.05475784862496958</v>
       </c>
       <c r="X3">
-        <v>0.1045295470348424</v>
+        <v>0.0926791772676728</v>
       </c>
       <c r="Y3">
-        <v>-0.3654214852852712</v>
+        <v>-0.1474370258926424</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>-8.27985896318345</v>
       </c>
       <c r="AB3">
-        <v>0.1040172433283613</v>
+        <v>0.08855940134754284</v>
+      </c>
+      <c r="AC3">
+        <v>-8.368418364530994</v>
       </c>
       <c r="AD3">
         <v>0</v>
       </c>
       <c r="AE3">
-        <v>9.902398459282114</v>
+        <v>22.24039121429266</v>
       </c>
       <c r="AF3">
-        <v>9.902398459282114</v>
+        <v>22.24039121429266</v>
       </c>
       <c r="AG3">
-        <v>-406.4976015407179</v>
+        <v>-277.1596087857073</v>
       </c>
       <c r="AH3">
-        <v>0.008100105547246446</v>
+        <v>0.07846584997647002</v>
       </c>
       <c r="AI3">
-        <v>0.02353218160243042</v>
+        <v>0.03386997131438198</v>
       </c>
       <c r="AJ3">
-        <v>-0.5042753902204782</v>
+        <v>17.36631596094754</v>
       </c>
       <c r="AK3">
-        <v>-92.33548605389205</v>
+        <v>-0.7758350276227626</v>
       </c>
       <c r="AL3">
-        <v>0.045</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.345</v>
+        <v>-7.73</v>
       </c>
       <c r="AN3">
         <v>-0</v>
       </c>
-      <c r="AO3">
-        <v>-2337.777777777778</v>
-      </c>
       <c r="AP3">
-        <v>3.943133199541351</v>
+        <v>2.09874003320996</v>
       </c>
       <c r="AQ3">
-        <v>304.9275362318841</v>
+        <v>17.78783958602846</v>
       </c>
     </row>
   </sheetData>
